--- a/漢字（かんじ）/h.xlsx
+++ b/漢字（かんじ）/h.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="は" sheetId="1" r:id="rId1"/>
@@ -320,7 +320,8 @@
     <t>費</t>
   </si>
   <si>
-    <t>費用｜ひよう</t>
+    <t>費用｜ひよう
+浪費｜ろうひ</t>
   </si>
   <si>
     <t>ひつ</t>
@@ -432,6 +433,8 @@
   </si>
   <si>
     <t>食品｜しょくひん
+作品｜さくひん
+薬品｜やくひん
 品質｜ひんしつ
 上品｜じょうひん
 備蓄品｜びちくひん</t>
@@ -2047,7 +2050,7 @@
       <c r="B3" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>81</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -2207,7 +2210,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="16" ht="72" spans="1:7">
+    <row r="16" ht="108" spans="1:7">
       <c r="A16" s="1" t="s">
         <v>111</v>
       </c>

--- a/漢字（かんじ）/h.xlsx
+++ b/漢字（かんじ）/h.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="3"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="は" sheetId="1" r:id="rId1"/>
@@ -234,7 +234,8 @@
   <si>
     <t>造反｜ぞうはん
 反対｜はんたい
-反映｜はんえい</t>
+反映｜はんえい
+反省｜はんせい</t>
   </si>
   <si>
     <t>はは</t>
@@ -1886,7 +1887,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" ht="54" spans="1:7">
+    <row r="14" ht="72" spans="1:7">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>

--- a/漢字（かんじ）/h.xlsx
+++ b/漢字（かんじ）/h.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="は" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="178">
   <si>
     <t>仮名</t>
   </si>
@@ -204,6 +204,21 @@
     <t>大半｜たいはん
 半額｜はんがく
 半袖｜はんそで</t>
+  </si>
+  <si>
+    <t>薄</t>
+  </si>
+  <si>
+    <t>希薄｜きはく</t>
+  </si>
+  <si>
+    <t>反</t>
+  </si>
+  <si>
+    <t>造反｜ぞうはん
+反対｜はんたい
+反映｜はんえい
+反省｜はんせい</t>
   </si>
   <si>
     <t>はつ</t>
@@ -229,13 +244,13 @@
 揮発性｜きはつせい</t>
   </si>
   <si>
-    <t>反</t>
-  </si>
-  <si>
-    <t>造反｜ぞうはん
-反対｜はんたい
-反映｜はんえい
-反省｜はんせい</t>
+    <t>はい</t>
+  </si>
+  <si>
+    <t>背</t>
+  </si>
+  <si>
+    <t>背景｜はいけい</t>
   </si>
   <si>
     <t>はは</t>
@@ -245,21 +260,6 @@
   </si>
   <si>
     <t>母親｜ははおや</t>
-  </si>
-  <si>
-    <t>はい</t>
-  </si>
-  <si>
-    <t>背</t>
-  </si>
-  <si>
-    <t>背景｜はいけい</t>
-  </si>
-  <si>
-    <t>はし</t>
-  </si>
-  <si>
-    <t>橋</t>
   </si>
   <si>
     <t>敗</t>
@@ -269,16 +269,22 @@
 失敗｜しっぱい</t>
   </si>
   <si>
+    <t>はし</t>
+  </si>
+  <si>
+    <t>橋</t>
+  </si>
+  <si>
+    <t>灰</t>
+  </si>
+  <si>
+    <t>灰皿｜はいざら</t>
+  </si>
+  <si>
     <t>箸</t>
   </si>
   <si>
     <t>割箸｜わりばし</t>
-  </si>
-  <si>
-    <t>灰</t>
-  </si>
-  <si>
-    <t>灰皿｜はいざら</t>
   </si>
   <si>
     <t>配</t>
@@ -455,7 +461,8 @@
   <si>
     <t>評価｜ひょうか
 風評｜ふうひょう
-批評｜ひひょう</t>
+批評｜ひひょう
+好評｜こうひょう</t>
   </si>
   <si>
     <t>表</t>
@@ -465,6 +472,7 @@
 表彰｜ひょうしょう
 表示｜ひょうじ
 表面｜ひょうめん
+公表｜こうひょう
 辞表｜じひょう
 代表｜だいひょう
 価格表｜かかくひょう
@@ -1867,7 +1875,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" ht="270" spans="1:7">
+    <row r="13" ht="54" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>27</v>
       </c>
@@ -1878,55 +1886,58 @@
         <v>50</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" ht="72" spans="1:7">
+    </row>
+    <row r="14" ht="270" spans="1:7">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="E14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="15" ht="70.8" customHeight="1" spans="1:7">
       <c r="A15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="16" ht="36" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>64</v>
@@ -1935,18 +1946,15 @@
         <v>65</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G16" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>68</v>
@@ -1954,38 +1962,47 @@
       <c r="C17" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="18" ht="108" spans="1:3">
+      <c r="E17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" ht="108" spans="1:7">
       <c r="A18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" ht="54" spans="1:3">
+    </row>
+    <row r="20" ht="54" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2026,73 +2043,73 @@
     </row>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" ht="87.6" customHeight="1" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" ht="53.4" customHeight="1" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" ht="36" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -2100,13 +2117,13 @@
     </row>
     <row r="6" ht="54" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -2114,156 +2131,156 @@
     </row>
     <row r="7" ht="36" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" ht="22.2" customHeight="1" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" ht="36" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" ht="36.6" customHeight="1" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" ht="36.6" customHeight="1" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" ht="108" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" ht="54" spans="1:3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" ht="72" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" ht="180" spans="1:3">
+      <c r="A19" s="1" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="19" ht="162" spans="1:3">
-      <c r="A19" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="B19" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -2297,131 +2314,131 @@
     </row>
     <row r="2" ht="18" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" ht="54" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" ht="57.6" customHeight="1" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" ht="20.4" customHeight="1" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" ht="36" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" ht="144" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" ht="36" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" ht="36" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -2463,129 +2480,129 @@
     </row>
     <row r="2" ht="108" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" ht="54" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" ht="90" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" ht="36" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" ht="90" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" ht="126" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" ht="54" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" ht="55.8" customHeight="1" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" ht="162" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
